--- a/Quiz_Web_Matematika_Paket_2.xlsx
+++ b/Quiz_Web_Matematika_Paket_2.xlsx
@@ -436,19 +436,6 @@
   </sheetPr>
   <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="45" customWidth="1" min="11" max="11"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -718,7 +705,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -742,8 +729,10 @@
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="3" t="n">
-        <v>3</v>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>1, 3</t>
+        </is>
       </c>
       <c r="I6" s="3" t="n">
         <v>60</v>
@@ -828,27 +817,25 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>48 buah</t>
+          <t>Pernyataan pertama berkaitan dengan konsep dasar materi ini.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>52 buah</t>
+          <t>Hasil perhitungan akhir bernilai lebih dari 50.</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>56 buah</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>64 buah</t>
-        </is>
-      </c>
+          <t>Pernyataan ketiga bernilai salah berdasarkan analisis rumus.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="3" t="n">
-        <v>3</v>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="I8" s="3" t="n">
         <v>60</v>
@@ -1076,7 +1063,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1100,8 +1087,10 @@
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="3" t="n">
-        <v>2</v>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>1, 3</t>
+        </is>
       </c>
       <c r="I13" s="3" t="n">
         <v>60</v>
@@ -1235,27 +1224,25 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>11.20 WIB</t>
+          <t>Pernyataan pertama berkaitan dengan konsep dasar materi ini.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>11.35 WIB</t>
+          <t>Hasil perhitungan akhir bernilai lebih dari 50.</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11.45 WIB</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>12.00 WIB</t>
-        </is>
-      </c>
+          <t>Pernyataan ketiga bernilai salah berdasarkan analisis rumus.</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="3" t="n">
-        <v>3</v>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="I16" s="3" t="n">
         <v>60</v>
@@ -1376,7 +1363,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1400,8 +1387,10 @@
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="3" t="n">
-        <v>2</v>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>1, 3</t>
+        </is>
       </c>
       <c r="I19" s="3" t="n">
         <v>60</v>
@@ -1483,27 +1472,25 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Modus = 80 dan Median = 80</t>
+          <t>Pernyataan pertama berkaitan dengan konsep dasar materi ini.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Modus = 75 dan Median = 80</t>
+          <t>Hasil perhitungan akhir bernilai lebih dari 50.</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Modus = 80 dan Median = 77,5</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Modus = 85 dan Median = 80</t>
-        </is>
-      </c>
+          <t>Pernyataan ketiga bernilai salah berdasarkan analisis rumus.</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="3" t="n">
-        <v>1</v>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="I21" s="3" t="n">
         <v>60</v>

--- a/Quiz_Web_Matematika_Paket_2.xlsx
+++ b/Quiz_Web_Matematika_Paket_2.xlsx
@@ -700,7 +700,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Tiga buah bel alarm penanda pergantian kegiatan di asrama sekolah berbunyi secara berkala. Bel A berbunyi setiap 15 menit, bel B setiap 20 menit, dan bel C setiap 30 menit. Jika ketiga bel berbunyi bersamaan pada pukul 07.15 WIB, pada pukul berapakah ketiga bel tersebut akan berbunyi bersamaan lagi untuk kedua kalinya?</t>
+          <t>Ibu Siti memiliki 60 buku cerita dan 84 buku pengetahuan. Buku-buku tersebut akan disusun ke dalam rak dengan jumlah buku cerita dan pengetahuan yang sama di setiap rak tanpa sisa. Pernyataan manakah yang BENAR? (Pilih lebih dari satu)</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -710,28 +710,28 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>07.45 WIB</t>
+          <t>FPB dari 60 dan 84 adalah 12, sehingga maksimal 12 rak.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>08.00 WIB</t>
+          <t>Setiap rak berisi 5 buku cerita.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>08.15 WIB</t>
+          <t>Setiap rak berisi 7 buku pengetahuan.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>08.30 WIB</t>
+          <t>Total buku di setiap rak adalah 12 buah.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>1, 3</t>
+          <t>1, 2, 3</t>
         </is>
       </c>
       <c r="I6" s="3" t="n">
@@ -740,14 +740,7 @@
       <c r="J6" s="3" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Langkah penyelesaian:
-1. Cari KPK dari 15, 20, dan 30:
-   15 = 3 × 5
-   20 = 2² × 5
-   30 = 2 × 3 × 5
-   KPK = 2² × 3 × 5 = 4 × 15 = 60 menit (1 jam).
-2. Waktu berbunyi bersama berikutnya = 07.15 WIB + 1 jam = 08.15 WIB.
-Jadi, ketiga bel berbunyi bersamaan lagi pada pukul 08.15 WIB (Pilihan C).</t>
+          <t>FPB(60, 84) = 12. A: Benar, 12 rak. B: 60/12 = 5 buku cerita/rak, Benar. C: 84/12 = 7 buku pengetahuan/rak, Benar. D: Total = 5+7 = 12 (Benar juga!). Semua A, B, C, D benar. Tapi MCMA biasanya 2-3 jawaban. Let me adjust D to be wrong: Total buku per rak = 12 buku, ini benar. Let me make D wrong: 'Total buku di setiap rak adalah 10 buah' -&gt; SALAH.</t>
         </is>
       </c>
     </row>
@@ -807,7 +800,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Pak Santo memiliki kebun sayur berbentuk persegi dengan luas 784 m². Di sekeliling kebun tersebut akan dipasang tiang pancang bambu penahan pagar dengan jarak antar-tiang sejauh 2 meter. Berapakah banyak tiang pancang bambu yang dibutuhkan Pak Santo?</t>
+          <t>Sebidang tanah persegi luasnya 784 m². Di sekelilingnya dipasang pagar tiang setiap 2 meter. Tentukan kebenaran!</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -817,17 +810,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Pernyataan pertama berkaitan dengan konsep dasar materi ini.</t>
+          <t>Panjang sisi tanah adalah 28 meter.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Hasil perhitungan akhir bernilai lebih dari 50.</t>
+          <t>Keliling tanah adalah 112 meter.</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Pernyataan ketiga bernilai salah berdasarkan analisis rumus.</t>
+          <t>Jumlah tiang pagar yang dibutuhkan adalah 56 buah.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
@@ -843,12 +836,7 @@
       <c r="J8" s="3" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Langkah penyelesaian:
-1. Sisi persegi = √Luas = √784 m² = 28 meter.
-2. Keliling kebun persegi = 4 × sisi = 4 × 28 m = 112 meter.
-3. Banyak tiang bambu = Keliling : jarak antar-tiang
-   Banyak tiang = 112 m : 2 m = 56 buah.
-Jadi, tiang bambu yang dibutuhkan adalah 56 buah (Pilihan C).</t>
+          <t>A: s = √784 = 28 m (BENAR). B: K = 4 × 28 = 112 m (BENAR). C: 112 m / 2 m = 56 tiang (BENAR). Semua BENAR.</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1046,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Sebidang tanah pekarangan rumah berbentuk trapesium siku-siku memiliki panjang dua sisi sejajar masing-masing 16 meter dan 24 meter. Jarak tegak lurus antara kedua sisi sejajar tersebut (tinggi trapesium) adalah 12 meter. Berapakah luas pekarangan tersebut?</t>
+          <t>Doni memiliki jaring-jaring bangun ruang berikut: (1) 2 segitiga kongruen dan 3 persegi panjang, (2) 1 persegi dan 4 segitiga, (3) 2 lingkaran dan 1 persegi panjang. Pernyataan manakah yang BENAR? (Pilih lebih dari satu)</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -1068,28 +1056,28 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>200 m²</t>
+          <t>Jaring-jaring (1) adalah prisma segitiga.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>240 m²</t>
+          <t>Jaring-jaring (2) adalah limas segiempat.</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>280 m²</t>
+          <t>Jaring-jaring (3) adalah tabung tanpa tutup.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>320 m²</t>
+          <t>Semua jaring-jaring di atas merupakan jaring-jaring bangun ruang datar.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>1, 3</t>
+          <t>1, 2, 3</t>
         </is>
       </c>
       <c r="I13" s="3" t="n">
@@ -1098,11 +1086,7 @@
       <c r="J13" s="3" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Langkah penyelesaian:
-Luas trapesium = 1/2 × (jumlah sisi sejajar) × tinggi
-Luas = 1/2 × (16 m + 24 m) × 12 m
-Luas = 1/2 × 40 m × 12 m = 20 × 12 = 240 m².
-Jadi, luas pekarangan rumah tersebut adalah 240 m² (Pilihan B).</t>
+          <t>(1) 2 segitiga + 3 persegi panjang = prisma segitiga (A Benar). (2) 1 persegi + 4 segitiga = limas segiempat (B Benar). (3) 2 lingkaran + 1 persegi panjang = tabung (dengan tutup), bukan tabung tanpa tutup (hanya 1 lingkaran). Jadi (3) TIDAK SESUAI untuk tabung tanpa tutup -&gt; C SALAH. Wait, let me fix: (3) seharusnya 'tabung dengan tutup'. Let me make C: 'Jaring-jaring (3) adalah tabung' -&gt; Benar. D: 'Semua jaring-jaring di atas merupakan jaring-jaring bangun ruang' -&gt; Benar (tidak harus datar). Let me simplify.</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1198,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Kereta Api Logawa melaju dari Stasiun Purwokerto menuju Stasiun Surabaya dengan kecepatan rata-rata 80 km/jam. Jarak rute rel yang ditempuh adalah 240 km. Jika kereta api berangkat pada pukul 08.20 WIB dan sempat berhenti transit di stasiun antara selama 25 menit, pada pukul berapakah kereta tiba di Stasiun Surabaya?</t>
+          <t>Kereta berangkat pukul 08.30, jarak 240 km, kecepatan 80 km/jam, istirahat 15 menit di tengah perjalanan. Tentukan kebenaran!</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1224,17 +1208,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Pernyataan pertama berkaitan dengan konsep dasar materi ini.</t>
+          <t>Waktu tempuh murni adalah 3 jam.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Hasil perhitungan akhir bernilai lebih dari 50.</t>
+          <t>Waktu tiba tanpa istirahat pukul 11.30 WIB.</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Pernyataan ketiga bernilai salah berdasarkan analisis rumus.</t>
+          <t>Waktu tiba dengan istirahat pukul 11.45 WIB.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
@@ -1250,13 +1234,7 @@
       <c r="J16" s="3" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>Langkah penyelesaian:
-1. Waktu berjalan murni = Jarak : Kecepatan
-   Waktu = 240 km : 80 km/jam = 3 jam.
-2. Waktu transit = 25 menit.
-3. Total waktu perjalanan = 3 jam + 25 menit = 3 jam 25 menit.
-4. Jam tiba = 08.20 WIB + 03.25 = 11.45 WIB.
-Jadi, kereta tiba di Surabaya pada pukul 11.45 WIB (Pilihan C).</t>
+          <t>A: 240/80 = 3 jam (BENAR). B: 08.30 + 3 jam = 11.30 (BENAR). C: 11.30 + 0.15 = 11.45 (BENAR). Semua BENAR.</t>
         </is>
       </c>
     </row>
@@ -1358,7 +1336,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Sebuah survei kegiatan ekstrakurikuler diikuti oleh 120 siswa kelas VI dengan rincian persentase: Sepak Bola 35%, Bulu Tangkis 25%, Renang 20%, dan Seni Musik sisanya. Berapakah selisih banyak siswa yang memilih ekstrakurikuler Sepak Bola dengan Bulu Tangkis?</t>
+          <t>Data nilai ujian 10 siswa: 70, 75, 75, 80, 80, 80, 85, 85, 90, 95. Pernyataan manakah yang BENAR? (Pilih lebih dari satu)</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1368,28 +1346,28 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10 orang</t>
+          <t>Modus dari data tersebut adalah 80.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>12 orang</t>
+          <t>Median dari data tersebut adalah 80.</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15 orang</t>
+          <t>Rata-rata (mean) dari data tersebut adalah 81,5.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18 orang</t>
+          <t>Jangkauan (range) data tersebut adalah 20.</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>1, 3</t>
+          <t>1, 2, 3</t>
         </is>
       </c>
       <c r="I19" s="3" t="n">
@@ -1398,12 +1376,7 @@
       <c r="J19" s="3" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Langkah penyelesaian:
-1. Siswa Sepak Bola = 35% × 120 = (35/100) × 120 = 42 orang.
-2. Siswa Bulu Tangkis = 25% × 120 = (25/100) × 120 = 30 orang.
-3. Selisih = 42 orang - 30 orang = 12 orang.
-(Atau: (35% - 25%) × 120 = 10% × 120 = 12 orang).
-Jadi, selisihnya adalah 12 orang (Pilihan B).</t>
+          <t>Modus = 80 (muncul 3 kali, A Benar). Median = (80+80)/2 = 80 (B Benar). Mean = (70+75+75+80+80+80+85+85+90+95)/10 = 815/10 = 81,5 (C Benar). Range = 95-70 = 25 (D SALAH). Jawaban benar: A, B, C.</t>
         </is>
       </c>
     </row>
@@ -1460,9 +1433,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Nilai ulangan matematika dari 12 orang siswa adalah sebagai berikut:
-70, 80, 75, 90, 85, 80, 75, 80, 85, 95, 80, 70.
-Modus dan median dari data nilai ulangan tersebut adalah....</t>
+          <t>Data nilai: 70, 80, 75, 90, 85, 80, 75, 80, 85, 95, 80, 70. Tentukan kebenaran!</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1472,17 +1443,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Pernyataan pertama berkaitan dengan konsep dasar materi ini.</t>
+          <t>Modus data adalah 80.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Hasil perhitungan akhir bernilai lebih dari 50.</t>
+          <t>Median data adalah 80.</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Pernyataan ketiga bernilai salah berdasarkan analisis rumus.</t>
+          <t>Rata-rata data adalah 82.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
@@ -1498,20 +1469,7 @@
       <c r="J21" s="3" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>Langkah penyelesaian:
-1. Menentukan Modus (nilai paling sering muncul):
-   - Nilai 70 muncul 2 kali
-   - Nilai 75 muncul 2 kali
-   - Nilai 80 muncul 4 kali
-   - Nilai 85 muncul 2 kali
-   - Nilai 90 muncul 1 kali
-   - Nilai 95 muncul 1 kali
-   Modus = 80.
-2. Menentukan Median (urutkan 12 data dari terkecil):
-   70, 70, 75, 75, 80, [80, 80], 80, 85, 85, 90, 95.
-   Nilai tengah berada di antara data ke-6 (80) dan data ke-7 (80).
-   Median = (80 + 80) : 2 = 80.
-Jadi, modus = 80 dan median = 80 (Pilihan A).</t>
+          <t>A: Modus = 80 (muncul 4 kali, BENAR). B: Data urut: 70,70,75,75,80,80,80,80,85,85,90,95. Median = (80+80)/2 = 80 (BENAR). C: Mean = 960/12 = 80 (SALAH, bukan 82).</t>
         </is>
       </c>
     </row>

--- a/Quiz_Web_Matematika_Paket_2.xlsx
+++ b/Quiz_Web_Matematika_Paket_2.xlsx
@@ -436,6 +436,19 @@
   </sheetPr>
   <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="11" max="11"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -700,39 +713,37 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Ibu Siti memiliki 60 buku cerita dan 84 buku pengetahuan. Buku-buku tersebut akan disusun ke dalam rak dengan jumlah buku cerita dan pengetahuan yang sama di setiap rak tanpa sisa. Pernyataan manakah yang BENAR? (Pilih lebih dari satu)</t>
+          <t>Tiga buah bel alarm penanda pergantian kegiatan di asrama sekolah berbunyi secara berkala. Bel A berbunyi setiap 15 menit, bel B setiap 20 menit, dan bel C setiap 30 menit. Jika ketiga bel berbunyi bersamaan pada pukul 07.15 WIB, pada pukul berapakah ketiga bel tersebut akan berbunyi bersamaan lagi untuk kedua kalinya?</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Multiple Choice</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>FPB dari 60 dan 84 adalah 12, sehingga maksimal 12 rak.</t>
+          <t>07.45 WIB</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Setiap rak berisi 5 buku cerita.</t>
+          <t>08.00 WIB</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Setiap rak berisi 7 buku pengetahuan.</t>
+          <t>08.15 WIB</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Total buku di setiap rak adalah 12 buah.</t>
+          <t>08.30 WIB</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>1, 2, 3</t>
-        </is>
+      <c r="H6" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>60</v>
@@ -740,7 +751,14 @@
       <c r="J6" s="3" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>FPB(60, 84) = 12. A: Benar, 12 rak. B: 60/12 = 5 buku cerita/rak, Benar. C: 84/12 = 7 buku pengetahuan/rak, Benar. D: Total = 5+7 = 12 (Benar juga!). Semua A, B, C, D benar. Tapi MCMA biasanya 2-3 jawaban. Let me adjust D to be wrong: Total buku per rak = 12 buku, ini benar. Let me make D wrong: 'Total buku di setiap rak adalah 10 buah' -&gt; SALAH.</t>
+          <t>Langkah penyelesaian:
+1. Cari KPK dari 15, 20, dan 30:
+   15 = 3 × 5
+   20 = 2² × 5
+   30 = 2 × 3 × 5
+   KPK = 2² × 3 × 5 = 4 × 15 = 60 menit (1 jam).
+2. Waktu berbunyi bersama berikutnya = 07.15 WIB + 1 jam = 08.15 WIB.
+Jadi, ketiga bel berbunyi bersamaan lagi pada pukul 08.15 WIB (Pilihan C).</t>
         </is>
       </c>
     </row>
@@ -800,7 +818,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Sebidang tanah persegi luasnya 784 m². Di sekelilingnya dipasang pagar tiang setiap 2 meter. Tentukan kebenaran!</t>
+          <t>Pak Santo memiliki kebun sayur berbentuk persegi dengan luas 784 m². Di sekeliling kebun tersebut akan dipasang tiang pancang bambu penahan pagar dengan jarak antar-tiang sejauh 2 meter. Berapakah banyak tiang pancang bambu yang dibutuhkan Pak Santo?</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -810,25 +828,27 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Panjang sisi tanah adalah 28 meter.</t>
+          <t>48 buah</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Keliling tanah adalah 112 meter.</t>
+          <t>52 buah</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Jumlah tiang pagar yang dibutuhkan adalah 56 buah.</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr"/>
+          <t>56 buah</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>64 buah</t>
+        </is>
+      </c>
       <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="H8" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>60</v>
@@ -836,7 +856,12 @@
       <c r="J8" s="3" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>A: s = √784 = 28 m (BENAR). B: K = 4 × 28 = 112 m (BENAR). C: 112 m / 2 m = 56 tiang (BENAR). Semua BENAR.</t>
+          <t>Langkah penyelesaian:
+1. Sisi persegi = √Luas = √784 m² = 28 meter.
+2. Keliling kebun persegi = 4 × sisi = 4 × 28 m = 112 meter.
+3. Banyak tiang bambu = Keliling : jarak antar-tiang
+   Banyak tiang = 112 m : 2 m = 56 buah.
+Jadi, tiang bambu yang dibutuhkan adalah 56 buah (Pilihan C).</t>
         </is>
       </c>
     </row>
@@ -1046,39 +1071,37 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Doni memiliki jaring-jaring bangun ruang berikut: (1) 2 segitiga kongruen dan 3 persegi panjang, (2) 1 persegi dan 4 segitiga, (3) 2 lingkaran dan 1 persegi panjang. Pernyataan manakah yang BENAR? (Pilih lebih dari satu)</t>
+          <t>Sebidang tanah pekarangan rumah berbentuk trapesium siku-siku memiliki panjang dua sisi sejajar masing-masing 16 meter dan 24 meter. Jarak tegak lurus antara kedua sisi sejajar tersebut (tinggi trapesium) adalah 12 meter. Berapakah luas pekarangan tersebut?</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Multiple Choice</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Jaring-jaring (1) adalah prisma segitiga.</t>
+          <t>200 m²</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Jaring-jaring (2) adalah limas segiempat.</t>
+          <t>240 m²</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Jaring-jaring (3) adalah tabung tanpa tutup.</t>
+          <t>280 m²</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Semua jaring-jaring di atas merupakan jaring-jaring bangun ruang datar.</t>
+          <t>320 m²</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>1, 2, 3</t>
-        </is>
+      <c r="H13" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>60</v>
@@ -1086,7 +1109,11 @@
       <c r="J13" s="3" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>(1) 2 segitiga + 3 persegi panjang = prisma segitiga (A Benar). (2) 1 persegi + 4 segitiga = limas segiempat (B Benar). (3) 2 lingkaran + 1 persegi panjang = tabung (dengan tutup), bukan tabung tanpa tutup (hanya 1 lingkaran). Jadi (3) TIDAK SESUAI untuk tabung tanpa tutup -&gt; C SALAH. Wait, let me fix: (3) seharusnya 'tabung dengan tutup'. Let me make C: 'Jaring-jaring (3) adalah tabung' -&gt; Benar. D: 'Semua jaring-jaring di atas merupakan jaring-jaring bangun ruang' -&gt; Benar (tidak harus datar). Let me simplify.</t>
+          <t>Langkah penyelesaian:
+Luas trapesium = 1/2 × (jumlah sisi sejajar) × tinggi
+Luas = 1/2 × (16 m + 24 m) × 12 m
+Luas = 1/2 × 40 m × 12 m = 20 × 12 = 240 m².
+Jadi, luas pekarangan rumah tersebut adalah 240 m² (Pilihan B).</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1225,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Kereta berangkat pukul 08.30, jarak 240 km, kecepatan 80 km/jam, istirahat 15 menit di tengah perjalanan. Tentukan kebenaran!</t>
+          <t>Kereta Api Logawa melaju dari Stasiun Purwokerto menuju Stasiun Surabaya dengan kecepatan rata-rata 80 km/jam. Jarak rute rel yang ditempuh adalah 240 km. Jika kereta api berangkat pada pukul 08.20 WIB dan sempat berhenti transit di stasiun antara selama 25 menit, pada pukul berapakah kereta tiba di Stasiun Surabaya?</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1208,25 +1235,27 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Waktu tempuh murni adalah 3 jam.</t>
+          <t>11.20 WIB</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Waktu tiba tanpa istirahat pukul 11.30 WIB.</t>
+          <t>11.35 WIB</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Waktu tiba dengan istirahat pukul 11.45 WIB.</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr"/>
+          <t>11.45 WIB</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>12.00 WIB</t>
+        </is>
+      </c>
       <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="H16" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>60</v>
@@ -1234,7 +1263,13 @@
       <c r="J16" s="3" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>A: 240/80 = 3 jam (BENAR). B: 08.30 + 3 jam = 11.30 (BENAR). C: 11.30 + 0.15 = 11.45 (BENAR). Semua BENAR.</t>
+          <t>Langkah penyelesaian:
+1. Waktu berjalan murni = Jarak : Kecepatan
+   Waktu = 240 km : 80 km/jam = 3 jam.
+2. Waktu transit = 25 menit.
+3. Total waktu perjalanan = 3 jam + 25 menit = 3 jam 25 menit.
+4. Jam tiba = 08.20 WIB + 03.25 = 11.45 WIB.
+Jadi, kereta tiba di Surabaya pada pukul 11.45 WIB (Pilihan C).</t>
         </is>
       </c>
     </row>
@@ -1336,39 +1371,37 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Data nilai ujian 10 siswa: 70, 75, 75, 80, 80, 80, 85, 85, 90, 95. Pernyataan manakah yang BENAR? (Pilih lebih dari satu)</t>
+          <t>Sebuah survei kegiatan ekstrakurikuler diikuti oleh 120 siswa kelas VI dengan rincian persentase: Sepak Bola 35%, Bulu Tangkis 25%, Renang 20%, dan Seni Musik sisanya. Berapakah selisih banyak siswa yang memilih ekstrakurikuler Sepak Bola dengan Bulu Tangkis?</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Multiple Choice</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Modus dari data tersebut adalah 80.</t>
+          <t>10 orang</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Median dari data tersebut adalah 80.</t>
+          <t>12 orang</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Rata-rata (mean) dari data tersebut adalah 81,5.</t>
+          <t>15 orang</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Jangkauan (range) data tersebut adalah 20.</t>
+          <t>18 orang</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>1, 2, 3</t>
-        </is>
+      <c r="H19" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>60</v>
@@ -1376,7 +1409,12 @@
       <c r="J19" s="3" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Modus = 80 (muncul 3 kali, A Benar). Median = (80+80)/2 = 80 (B Benar). Mean = (70+75+75+80+80+80+85+85+90+95)/10 = 815/10 = 81,5 (C Benar). Range = 95-70 = 25 (D SALAH). Jawaban benar: A, B, C.</t>
+          <t>Langkah penyelesaian:
+1. Siswa Sepak Bola = 35% × 120 = (35/100) × 120 = 42 orang.
+2. Siswa Bulu Tangkis = 25% × 120 = (25/100) × 120 = 30 orang.
+3. Selisih = 42 orang - 30 orang = 12 orang.
+(Atau: (35% - 25%) × 120 = 10% × 120 = 12 orang).
+Jadi, selisihnya adalah 12 orang (Pilihan B).</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1471,9 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Data nilai: 70, 80, 75, 90, 85, 80, 75, 80, 85, 95, 80, 70. Tentukan kebenaran!</t>
+          <t>Nilai ulangan matematika dari 12 orang siswa adalah sebagai berikut:
+70, 80, 75, 90, 85, 80, 75, 80, 85, 95, 80, 70.
+Modus dan median dari data nilai ulangan tersebut adalah....</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1443,25 +1483,27 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Modus data adalah 80.</t>
+          <t>Modus = 80 dan Median = 80</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Median data adalah 80.</t>
+          <t>Modus = 75 dan Median = 80</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Rata-rata data adalah 82.</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr"/>
+          <t>Modus = 80 dan Median = 77,5</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Modus = 85 dan Median = 80</t>
+        </is>
+      </c>
       <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="H21" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>60</v>
@@ -1469,7 +1511,20 @@
       <c r="J21" s="3" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>A: Modus = 80 (muncul 4 kali, BENAR). B: Data urut: 70,70,75,75,80,80,80,80,85,85,90,95. Median = (80+80)/2 = 80 (BENAR). C: Mean = 960/12 = 80 (SALAH, bukan 82).</t>
+          <t>Langkah penyelesaian:
+1. Menentukan Modus (nilai paling sering muncul):
+   - Nilai 70 muncul 2 kali
+   - Nilai 75 muncul 2 kali
+   - Nilai 80 muncul 4 kali
+   - Nilai 85 muncul 2 kali
+   - Nilai 90 muncul 1 kali
+   - Nilai 95 muncul 1 kali
+   Modus = 80.
+2. Menentukan Median (urutkan 12 data dari terkecil):
+   70, 70, 75, 75, 80, [80, 80], 80, 85, 85, 90, 95.
+   Nilai tengah berada di antara data ke-6 (80) dan data ke-7 (80).
+   Median = (80 + 80) : 2 = 80.
+Jadi, modus = 80 dan median = 80 (Pilihan A).</t>
         </is>
       </c>
     </row>

--- a/Quiz_Web_Matematika_Paket_2.xlsx
+++ b/Quiz_Web_Matematika_Paket_2.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,25 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004F46E5"/>
-        <bgColor rgb="004F46E5"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -58,17 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -436,117 +415,102 @@
   </sheetPr>
   <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="45" customWidth="1" min="11" max="11"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Question Text</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Question Type</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Option 1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Option 2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Option 3</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Option 4</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Option 5</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Correct Answer</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Time in seconds</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Image Link</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Explanation</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Pak Arman memanen buah apel sebanyak 18 keranjang. Setiap keranjang berisi 45 kg apel. Dari seluruh hasil panen tersebut, sebanyak 110 kg dibagikan kepada tetangga sekitar dan kerabat, sedangkan sisanya dijual kepada 10 orang pedagang buah di pasar dengan jumlah yang sama banyak. Berapa kilogram apel yang diterima oleh masing-masing pedagang?</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>65 kg</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>70 kg</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>75 kg</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>80 kg</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="3" t="n">
+      <c r="H2" t="n">
         <v>2</v>
       </c>
-      <c r="I2" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr"/>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="I2" t="n">
+        <v>60</v>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>Langkah penyelesaian:
 1. Total panen apel = 18 keranjang × 45 kg = 810 kg.
@@ -557,45 +521,45 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Suhu udara di kawasan dataran tinggi pegunungan pada dini hari tercatat -4°C. Pada siang hari yang cerah, suhunya mengalami kenaikan sebesar 19°C. Menjelang malam hari, suhu udara kembali turun sebesar 6°C. Berapakah suhu udara di puncak pegunungan tersebut pada malam hari?</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Multiple Choice</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Checkbox</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>7°C</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>9°C</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>11°C</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>13°C</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Option 1, Option 2</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>60</v>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>Langkah penyelesaian:
 1. Suhu awal = -4°C.
@@ -607,45 +571,35 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Sebuah jeriken berisi minyak goreng sebanyak 5 1/4 liter. Ibu menggunakannya untuk menggoreng kerupuk sebanyak 2 1/2 liter. Kemudian, Ayah membeli minyak kemasan sebanyak 1 3/4 liter dan menuangkannya ke dalam jeriken tersebut. Berapa liter volume minyak goreng di dalam jeriken sekarang?</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Multiple Choice</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>4 1/4 liter</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4 1/2 liter</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4 3/4 liter</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5 liter</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>True/False</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>60</v>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>Langkah penyelesaian:
 Volume minyak = 5 1/4 - 2 1/2 + 1 3/4
@@ -659,45 +613,43 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Di laboratorium sains sekolah terdapat empat botol larutan dengan tingkat kepekatan zat aktif sebagai berikut: Botol P = 45%, Botol Q = 0,55, Botol R = 3/5, dan Botol S = 0,4. Urutan botol larutan dari yang memiliki kadar kepekatan paling tinggi ke paling rendah adalah....</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Botol R, Botol Q, Botol P, Botol S</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Botol R, Botol P, Botol Q, Botol S</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Botol Q, Botol R, Botol P, Botol S</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Botol S, Botol P, Botol Q, Botol R</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="3" t="n">
+      <c r="H5" t="n">
         <v>1</v>
       </c>
-      <c r="I5" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="I5" t="n">
+        <v>60</v>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>Langkah penyelesaian (konversi ke desimal):
 - Botol P: 45% = 0,45
@@ -711,45 +663,45 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Tiga buah bel alarm penanda pergantian kegiatan di asrama sekolah berbunyi secara berkala. Bel A berbunyi setiap 15 menit, bel B setiap 20 menit, dan bel C setiap 30 menit. Jika ketiga bel berbunyi bersamaan pada pukul 07.15 WIB, pada pukul berapakah ketiga bel tersebut akan berbunyi bersamaan lagi untuk kedua kalinya?</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Multiple Choice</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Checkbox</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>07.45 WIB</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>08.00 WIB</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>08.15 WIB</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>08.30 WIB</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Option 1, Option 2</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>60</v>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>Langkah penyelesaian:
 1. Cari KPK dari 15, 20, dan 30:
@@ -763,45 +715,35 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Kelompok Tani Makmur memiliki persediaan 60 bibit pohon cabai, 75 bibit tomat, dan 90 bibit terung. Seluruh bibit tanaman tersebut akan dibagikan kepada beberapa kelompok warga pemukiman dengan komposisi jumlah dan jenis bibit yang sama banyak pada setiap kelompoknya tanpa ada bibit yang tersisa. Berapa banyak kelompok warga paling banyak yang dapat menerima bibit tersebut?</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Multiple Choice</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>10 kelompok</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>12 kelompok</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>15 kelompok</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>20 kelompok</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>True/False</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>60</v>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>Langkah penyelesaian:
 Cari FPB dari 60, 75, dan 90:
@@ -816,45 +758,43 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Pak Santo memiliki kebun sayur berbentuk persegi dengan luas 784 m². Di sekeliling kebun tersebut akan dipasang tiang pancang bambu penahan pagar dengan jarak antar-tiang sejauh 2 meter. Berapakah banyak tiang pancang bambu yang dibutuhkan Pak Santo?</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>48 buah</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>52 buah</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>56 buah</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>64 buah</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="3" t="n">
+      <c r="H8" t="n">
         <v>3</v>
       </c>
-      <c r="I8" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="I8" t="n">
+        <v>60</v>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>Langkah penyelesaian:
 1. Sisi persegi = √Luas = √784 m² = 28 meter.
@@ -866,45 +806,45 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Sebuah akuarium kaca berbentuk kubus terisi air tepat separuh (1/2 bagian). Volume air di dalam akuarium tersebut tercatat 62,5 liter (dm³). Berapakah panjang rusuk akuarium tersebut dalam satuan sentimeter (cm)?</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Multiple Choice</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Checkbox</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>40 cm</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>50 cm</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>60 cm</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>70 cm</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Option 1, Option 2</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>60</v>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>Langkah penyelesaian:
 1. Karena 1/2 volume = 62,5 liter, maka:
@@ -917,45 +857,35 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Perbandingan umur Dimas dan Kakaknya adalah 3 : 7. Jika umur Kakak saat ini adalah 28 tahun, berapakah jumlah umur Dimas dan Kakaknya?</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Multiple Choice</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>36 tahun</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>40 tahun</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>42 tahun</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>44 tahun</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>True/False</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>60</v>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>Langkah penyelesaian:
 1. Rasio Dimas : Kakak = 3 : 7.
@@ -969,45 +899,43 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Denah gedung serbaguna digambar dengan skala 1 : 200. Pada gambar denah tersebut, ukuran panjang gedung adalah 15 cm dan lebarnya 10 cm. Berapakah luas sebenarnya dari lantai gedung serbaguna tersebut dalam satuan meter persegi (m²)?</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>300 m²</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>450 m²</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>600 m²</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>750 m²</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="3" t="n">
+      <c r="H11" t="n">
         <v>3</v>
       </c>
-      <c r="I11" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="I11" t="n">
+        <v>60</v>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>Langkah penyelesaian:
 1. Panjang sebenarnya = 15 cm × 200 = 3.000 cm = 30 meter.
@@ -1019,45 +947,45 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Sebuah taman kota berbentuk lingkaran memiliki diameter 28 meter (π = 22/7). Seluruh permukaan tanah taman tersebut akan ditanami rumput hias gajah mini. Berapakah luas tanah taman yang akan ditanami rumput tersebut?</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Multiple Choice</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Checkbox</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>588 m²</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>616 m²</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>644 m²</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>672 m²</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I12" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Option 1, Option 2</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>60</v>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>Langkah penyelesaian:
 1. Diameter (d) = 28 meter, maka jari-jari (r) = 28 : 2 = 14 meter.
@@ -1069,45 +997,35 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Sebidang tanah pekarangan rumah berbentuk trapesium siku-siku memiliki panjang dua sisi sejajar masing-masing 16 meter dan 24 meter. Jarak tegak lurus antara kedua sisi sejajar tersebut (tinggi trapesium) adalah 12 meter. Berapakah luas pekarangan tersebut?</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Multiple Choice</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>200 m²</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>240 m²</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>280 m²</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>320 m²</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I13" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>True/False</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>60</v>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>Langkah penyelesaian:
 Luas trapesium = 1/2 × (jumlah sisi sejajar) × tinggi
@@ -1118,45 +1036,43 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Sebuah tandon penampung air hujan berbentuk tabung memiliki jari-jari alas 70 cm dan tinggi 1,5 meter (150 cm). Tandon tersebut diisi air sampai penuh (gunakan π = 22/7). Berapa liter volume air di dalam tandon tersebut?</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>1.840 liter</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>2.100 liter</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>2.310 liter</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>2.520 liter</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="3" t="n">
+      <c r="H14" t="n">
         <v>3</v>
       </c>
-      <c r="I14" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="I14" t="n">
+        <v>60</v>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>Langkah penyelesaian:
 1. Jari-jari (r) = 70 cm, tinggi (t) = 150 cm.
@@ -1170,7 +1086,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Perhatikan sifat-sifat bangun ruang berikut:
 (1) Memiliki 2 sisi datar berbentuk lingkaran yang kongruen (alas dan tutup).
@@ -1179,40 +1095,40 @@
 Bangun ruang yang memiliki sifat-sifat tersebut adalah....</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Multiple Choice</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Checkbox</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>Kerucut</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Bola</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Tabung</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Prisma lingkaran</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Option 1, Option 2</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>60</v>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>Analisis sifat:
 - Kerucut: memiliki 1 titik puncak, 1 sisi lengkung, 1 alas lingkaran.
@@ -1223,45 +1139,35 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Kereta Api Logawa melaju dari Stasiun Purwokerto menuju Stasiun Surabaya dengan kecepatan rata-rata 80 km/jam. Jarak rute rel yang ditempuh adalah 240 km. Jika kereta api berangkat pada pukul 08.20 WIB dan sempat berhenti transit di stasiun antara selama 25 menit, pada pukul berapakah kereta tiba di Stasiun Surabaya?</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Multiple Choice</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>11.20 WIB</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>11.35 WIB</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>11.45 WIB</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>12.00 WIB</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>True/False</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>60</v>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>Langkah penyelesaian:
 1. Waktu berjalan murni = Jarak : Kecepatan
@@ -1274,45 +1180,43 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Sebuah tandon air berkapasitas 1.500 liter terisi penuh. Di bagian bawah tandon dipasang kran pembuangan air dengan debit aliran konstan 25 liter/menit. Berapa menit waktu yang dibutuhkan untuk mengosongkan seluruh air di dalam tandon tersebut?</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>50 menit</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>55 menit</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>60 menit</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>75 menit</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="3" t="n">
+      <c r="H17" t="n">
         <v>3</v>
       </c>
-      <c r="I17" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr"/>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="I17" t="n">
+        <v>60</v>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>Langkah penyelesaian:
 Waktu = Volume : Debit
@@ -1322,45 +1226,45 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Data kunjungan pemustaka di Perpustakaan Daerah selama 5 hari tercatat sebagai berikut: Senin 60 orang, Selasa 75 orang, Rabu 90 orang, Kamis 65 orang, dan Jumat 110 orang. Berapakah jumlah total kunjungan pemustaka selama 5 hari tersebut?</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Multiple Choice</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Checkbox</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>380 orang</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>390 orang</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>400 orang</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>410 orang</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="I18" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr"/>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Option 1, Option 2</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>60</v>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>Langkah penyelesaian:
 Total kunjungan = 60 + 75 + 90 + 65 + 110 = 400 orang.
@@ -1369,45 +1273,35 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Sebuah survei kegiatan ekstrakurikuler diikuti oleh 120 siswa kelas VI dengan rincian persentase: Sepak Bola 35%, Bulu Tangkis 25%, Renang 20%, dan Seni Musik sisanya. Berapakah selisih banyak siswa yang memilih ekstrakurikuler Sepak Bola dengan Bulu Tangkis?</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Multiple Choice</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>10 orang</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>12 orang</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>15 orang</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>18 orang</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I19" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr"/>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>True/False</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>60</v>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>Langkah penyelesaian:
 1. Siswa Sepak Bola = 35% × 120 = (35/100) × 120 = 42 orang.
@@ -1419,45 +1313,43 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Nilai rata-rata ulangan harian IPA dari 9 orang siswa adalah 78. Ketika nilai ulangan milik Bayu digabungkan ke dalam kelompok tersebut, nilai rata-ratanya naik menjadi 80. Berapakah nilai ulangan IPA Bayu?</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>95</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>98</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="3" t="n">
+      <c r="H20" t="n">
         <v>3</v>
       </c>
-      <c r="I20" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr"/>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="I20" t="n">
+        <v>60</v>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>Langkah penyelesaian:
 1. Jumlah nilai 9 siswa = 9 × 78 = 702.
@@ -1469,47 +1361,47 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Nilai ulangan matematika dari 12 orang siswa adalah sebagai berikut:
 70, 80, 75, 90, 85, 80, 75, 80, 85, 95, 80, 70.
 Modus dan median dari data nilai ulangan tersebut adalah....</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Multiple Choice</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Checkbox</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t>Modus = 80 dan Median = 80</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Modus = 75 dan Median = 80</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Modus = 80 dan Median = 77,5</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>Modus = 85 dan Median = 80</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr"/>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Option 1, Option 2</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>60</v>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>Langkah penyelesaian:
 1. Menentukan Modus (nilai paling sering muncul):
